--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.95631</v>
+        <v>16.60978</v>
       </c>
       <c r="D2" t="n">
-        <v>16.66321</v>
+        <v>16.5171</v>
       </c>
       <c r="E2" t="n">
-        <v>16.90566</v>
+        <v>16.54867</v>
       </c>
       <c r="F2" t="n">
-        <v>41.9854</v>
+        <v>41.91842</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05081</v>
+        <v>0.05059</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81945</v>
+        <v>1.85407</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.9255</v>
+        <v>16.67277</v>
       </c>
       <c r="D3" t="n">
-        <v>16.72776</v>
+        <v>16.51821</v>
       </c>
       <c r="E3" t="n">
-        <v>16.65127</v>
+        <v>16.56248</v>
       </c>
       <c r="F3" t="n">
-        <v>42.84658</v>
+        <v>42.71624</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05061</v>
+        <v>0.05097</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79585</v>
+        <v>1.81938</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.93824</v>
+        <v>17.10885</v>
       </c>
       <c r="D4" t="n">
-        <v>16.88468</v>
+        <v>16.70245</v>
       </c>
       <c r="E4" t="n">
-        <v>16.50462</v>
+        <v>16.77693</v>
       </c>
       <c r="F4" t="n">
-        <v>42.4651</v>
+        <v>42.48018</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05044</v>
+        <v>0.05105</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81302</v>
+        <v>1.80524</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.48123</v>
+        <v>16.88887</v>
       </c>
       <c r="D6" t="n">
-        <v>16.15142</v>
+        <v>16.40523</v>
       </c>
       <c r="E6" t="n">
-        <v>16.6805</v>
+        <v>16.79531</v>
       </c>
       <c r="F6" t="n">
-        <v>22.25852</v>
+        <v>21.64813</v>
       </c>
       <c r="G6" t="n">
-        <v>33.83488</v>
+        <v>34.21949</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.39379</v>
+        <v>16.66672</v>
       </c>
       <c r="D7" t="n">
-        <v>16.29109</v>
+        <v>15.94134</v>
       </c>
       <c r="E7" t="n">
-        <v>16.63907</v>
+        <v>16.42477</v>
       </c>
       <c r="F7" t="n">
-        <v>21.49818</v>
+        <v>21.64332</v>
       </c>
       <c r="G7" t="n">
-        <v>34.58796</v>
+        <v>33.75398</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.79235</v>
+        <v>16.7444</v>
       </c>
       <c r="D8" t="n">
-        <v>16.13046</v>
+        <v>15.73165</v>
       </c>
       <c r="E8" t="n">
-        <v>16.54237</v>
+        <v>16.68818</v>
       </c>
       <c r="F8" t="n">
-        <v>22.31898</v>
+        <v>21.80237</v>
       </c>
       <c r="G8" t="n">
-        <v>33.71676</v>
+        <v>33.74255</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.60246</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14215</v>
+        <v>1.11642</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61648</v>
+        <v>0.60685</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10813</v>
+        <v>1.11115</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61622</v>
+        <v>0.61559</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11922</v>
+        <v>1.11159</v>
       </c>
     </row>
   </sheetData>
